--- a/Ristoranti_Viaggioperdue_master.xlsx
+++ b/Ristoranti_Viaggioperdue_master.xlsx
@@ -3603,7 +3603,7 @@
     <t>Spiaggia: attivo 9-12 e 15-18 · Emilia Romagna · 🌳 ·  ·</t>
   </si>
   <si>
-    <t>Massimo</t>
+    <t>Crotto del Sergente</t>
   </si>
   <si>
     <t>Via Crotto del Sergente 13</t>

--- a/Ristoranti_Viaggioperdue_master.xlsx
+++ b/Ristoranti_Viaggioperdue_master.xlsx
@@ -3603,7 +3603,7 @@
     <t>Spiaggia: attivo 9-12 e 15-18 · Emilia Romagna · 🌳 ·  ·</t>
   </si>
   <si>
-    <t>Crotto del Sergente</t>
+    <t>Massimo</t>
   </si>
   <si>
     <t>Via Crotto del Sergente 13</t>

--- a/Ristoranti_Viaggioperdue_master.xlsx
+++ b/Ristoranti_Viaggioperdue_master.xlsx
@@ -3444,7 +3444,7 @@
     <t>Pisa · Toscana · (DP)</t>
   </si>
   <si>
-    <t>Manuel Lombardi</t>
+    <t>H2O</t>
   </si>
   <si>
     <t>Via Pergola 10</t>
